--- a/TAM/Local_Government_TAM.xlsx
+++ b/TAM/Local_Government_TAM.xlsx
@@ -2333,13 +2333,13 @@
         <v>122</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>51</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>52</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C55" s="5" t="n">
         <v>587</v>
@@ -2612,7 +2612,7 @@
         <v>192</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>105</v>
@@ -4264,13 +4264,13 @@
         <v>93.90000000000001</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>649.7</v>
+        <v>644</v>
       </c>
       <c r="D103" s="11" t="n">
         <v>917.3</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>1930.2</v>
+        <v>1971.8</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>4932.7</v>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="B110" s="11" t="n">
-        <v>323.1</v>
+        <v>322.3</v>
       </c>
       <c r="C110" s="11" t="n">
         <v>1917</v>
@@ -4515,7 +4515,7 @@
         <v>2303.6</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>4121.5</v>
+        <v>4165.6</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>8858.200000000001</v>
@@ -22944,7 +22944,7 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" s="17" t="n">
         <v>2700</v>
@@ -22953,7 +22953,7 @@
         <v>2500</v>
       </c>
       <c r="E7" s="19" t="n">
-        <v>702000000</v>
+        <v>695250000</v>
       </c>
     </row>
     <row r="8">
@@ -22982,7 +22982,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>14000</v>
@@ -22991,7 +22991,7 @@
         <v>3500</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>1666000000</v>
+        <v>1715000000</v>
       </c>
     </row>
     <row r="10">
@@ -23063,7 +23063,7 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="n">
-        <v>21135800000</v>
+        <v>21178050000</v>
       </c>
     </row>
     <row r="15">
@@ -26492,7 +26492,7 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>450</v>
@@ -26501,7 +26501,7 @@
         <v>2000</v>
       </c>
       <c r="E6" s="19" t="n">
-        <v>188100000</v>
+        <v>187200000</v>
       </c>
     </row>
     <row r="7">
@@ -26549,7 +26549,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="17" t="n">
         <v>14000</v>
@@ -26558,7 +26558,7 @@
         <v>3500</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>2891000000</v>
+        <v>2940000000</v>
       </c>
     </row>
     <row r="10">
@@ -26630,7 +26630,7 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="n">
-        <v>36577250000</v>
+        <v>36625350000</v>
       </c>
     </row>
     <row r="15">
